--- a/Dashboard for lucky.xlsx
+++ b/Dashboard for lucky.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Ameet Computer\Desktop\Waseem\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADMIN\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D676AF41-C06D-40B4-9C59-6CDAC2DE6F5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F958C674-E17D-43C3-8CD2-99E9ACC6DC95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{A0CFAAF7-0A11-4445-83D0-076971652DD7}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{A0CFAAF7-0A11-4445-83D0-076971652DD7}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.00&quot;x&quot;"/>
-    <numFmt numFmtId="165" formatCode="#,##0.0;\(#,##0\);\-"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0;\(#,##0\);\-"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -149,7 +149,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -467,17 +467,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBA602DE-673E-45CD-A25C-21C14E8A44F5}">
   <dimension ref="B1:L23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="38" bestFit="1" customWidth="1"/>
-    <col min="3" max="5" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="5" width="11.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="12.54296875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.26953125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
@@ -521,7 +521,7 @@
         <v>2030</v>
       </c>
     </row>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B2" t="s">
         <v>11</v>
       </c>
@@ -556,7 +556,7 @@
         <v>212117290.58356571</v>
       </c>
     </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -591,7 +591,7 @@
         <v>9.4999999999999973E-2</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B4" t="s">
         <v>1</v>
       </c>
@@ -626,7 +626,7 @@
         <v>0.21250389249477716</v>
       </c>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
         <v>2</v>
       </c>
@@ -661,7 +661,7 @@
         <v>0.35103539338761752</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
         <v>3</v>
       </c>
@@ -696,7 +696,7 @@
         <v>0.35870265290655434</v>
       </c>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
         <v>4</v>
       </c>
@@ -731,7 +731,7 @@
         <v>0.30061208984122362</v>
       </c>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
         <v>5</v>
       </c>
@@ -766,7 +766,7 @@
         <v>-0.94025853136606463</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
         <v>6</v>
       </c>
@@ -801,7 +801,7 @@
         <v>2.4104185762731571</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
         <v>13</v>
       </c>
@@ -836,7 +836,7 @@
         <v>8.5775953494319507E-3</v>
       </c>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>7</v>
       </c>
@@ -871,12 +871,12 @@
         <v>0.12460920160330047</v>
       </c>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>9</v>
       </c>
@@ -911,7 +911,7 @@
         <v>3014637.1307674432</v>
       </c>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B15" t="s">
         <v>10</v>
       </c>
@@ -946,7 +946,7 @@
         <v>4.0486297877956948E-2</v>
       </c>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B16" t="s">
         <v>14</v>
       </c>
@@ -981,7 +981,7 @@
         <v>3102833</v>
       </c>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B17" t="s">
         <v>15</v>
       </c>
@@ -1016,7 +1016,7 @@
         <v>37463050.398653485</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B18" t="s">
         <v>16</v>
       </c>
@@ -1051,7 +1051,7 @@
         <v>73115119.372083619</v>
       </c>
     </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
       <c r="B19" t="s">
         <v>17</v>
       </c>
@@ -1086,7 +1086,7 @@
         <v>34344346.706396013</v>
       </c>
     </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C20" s="3"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -1098,12 +1098,12 @@
       <c r="K20" s="3"/>
       <c r="L20" s="3"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C21" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C22" s="3"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
@@ -1115,7 +1115,7 @@
       <c r="K22" s="3"/>
       <c r="L22" s="3"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
